--- a/public/templates/asset-import-template.xlsx
+++ b/public/templates/asset-import-template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>资产编号</t>
   </si>
@@ -66,7 +66,7 @@
     <t>ThinkPad X1 Carbon</t>
   </si>
   <si>
-    <t>PC</t>
+    <t>办公电脑</t>
   </si>
   <si>
     <t>20XS</t>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>资产导入模板</t>
-  </si>
-  <si>
-    <t>说明：品类列有下拉框，请从列表中选择</t>
   </si>
 </sst>
 </file>
@@ -251,7 +248,7 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
@@ -333,7 +330,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="无效品类" error="请从下拉列表中选择有效的资产品类" sqref="C3:C1000">
-      <formula1>"PC,PERIPHERAL,NETWORK,SERVER_STORAGE,MOBILE,MEETING,SECURITY_DEVICE,SECURITY_DOCUMENT,CUSTOM"</formula1>
+      <formula1>"办公电脑,外设配件,网络设备,服务器/存储,移动设备,会议设备,网络安全设备,安全文档,自定义类型"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
